--- a/outputs/patched_model_comparison.xlsx
+++ b/outputs/patched_model_comparison.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,388 +456,528 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>cv_aug_r2_std</t>
+          <t>test_mape</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>cv_baseline_mape</t>
+          <t>test_mape_std</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>cv_baseline_r2</t>
+          <t>test_r2</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>test_mape</t>
+          <t>test_r2_std</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>test_r2</t>
+          <t>test_mape_base</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>test_mape_base_std</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>test_r2_base</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>aug_delta_mape</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>aug_paired_p</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>Linear</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{"kernel": "rbf", "C": 100.0, "epsilon": 0.5, "gamma": "scale"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.680995325390169</v>
+        <v>7.354888394474983</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6590121096294085</v>
+        <v>1.241677961305935</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8159191516526692</v>
+        <v>-0.2867695450782776</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1848191467394336</v>
+        <v>7.354888394474983</v>
       </c>
       <c r="G2" t="n">
-        <v>3.192349317867136</v>
+        <v>1.241677961305935</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9228188546159697</v>
+        <v>-0.2867695450782776</v>
       </c>
       <c r="I2" t="n">
-        <v>3.730913363703954</v>
+        <v>2.033857286620624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9366079226911743</v>
+        <v>7.407134547829628</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.282835239117254</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.01652182340621948</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-0.05224615335464478</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.944051784244067</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": -1, "learning_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.38311106605815</v>
+        <v>7.008227184414864</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8382990760775433</v>
+        <v>1.806422563115009</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8399360434569649</v>
+        <v>-0.2156415700912476</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1572152092282791</v>
+        <v>7.943637371063232</v>
       </c>
       <c r="G3" t="n">
-        <v>17.18681314100454</v>
+        <v>1.871627610077855</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.09289231021999142</v>
+        <v>-1.231051051616669</v>
       </c>
       <c r="I3" t="n">
-        <v>4.239606191071443</v>
+        <v>3.866048182957782</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9189510929302428</v>
+        <v>8.902110978960991</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.289964027220917</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.0343830943107605</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-0.9584736078977585</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6306507586685342</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KAN</t>
+          <t>GaussianProcess</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{"width": [16, 1], "grid_size": 5, "spline_order": 3, "learning_rate": 0.01}</t>
+          <t>{"length_scale": 1.0, "noise": 0.1, "alpha": 1e-06}</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.917742535471916</v>
+        <v>8.274456265097012</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9213557588577448</v>
+        <v>2.372681136851306</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8311421632766723</v>
+        <v>-0.6485867791883132</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1503146684591974</v>
+        <v>8.27447217917957</v>
       </c>
       <c r="G4" t="n">
-        <v>2.740383930504322</v>
+        <v>2.372654986246685</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9602246522903443</v>
+        <v>-0.6485875341102467</v>
       </c>
       <c r="I4" t="n">
-        <v>4.594850167632103</v>
+        <v>2.648537059509777</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9105914235115051</v>
+        <v>5.075711952608027</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.43703874878553</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.7788256053121734</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.198760226571543</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.06418238360590016</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 20, "min_samples_split": 5}</t>
+          <t>{"n_estimators": 100, "max_depth": 6, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.695641247601482</v>
+        <v>8.101582489907742</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8554419330055419</v>
+        <v>3.210604968300438</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8371018538266615</v>
+        <v>-0.8935428142547608</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1482500276022976</v>
+        <v>8.655803799629211</v>
       </c>
       <c r="G5" t="n">
-        <v>2.569050499923363</v>
+        <v>2.984180922614528</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9612708431194695</v>
+        <v>-0.6746608018875122</v>
       </c>
       <c r="I5" t="n">
-        <v>4.641298521165874</v>
+        <v>2.664714483408999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9070974489282262</v>
+        <v>2.973991334438324</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.7123500170743982</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.8670162916183471</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5.681812465190887</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.01612151693718122</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>KAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 3, "learning_rate": 0.05}</t>
+          <t>{"width": [16, 1], "grid_size": 5, "spline_order": 3, "learning_rate": 0.01}</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4.515276957380676</v>
+        <v>8.681400418281555</v>
       </c>
       <c r="D6" t="n">
-        <v>1.100575854605122</v>
+        <v>2.347146236591373</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8452314358190025</v>
+        <v>-0.5991775274276734</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1417561775597533</v>
+        <v>8.681411892175674</v>
       </c>
       <c r="G6" t="n">
-        <v>2.653426461220055</v>
+        <v>2.347133761480238</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9653984666951946</v>
+        <v>-0.5991835594177246</v>
       </c>
       <c r="I6" t="n">
-        <v>5.20740452746288</v>
+        <v>2.476464437030267</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8817051510965267</v>
+        <v>3.233751766383648</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.8975368499784184</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8889954566955567</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5.447660125792027</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.009093906707337149</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 3, "learning_rate": 0.05}</t>
+          <t>{"n_estimators": 100, "max_depth": 2, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.513185136020184</v>
+        <v>8.969695066271132</v>
       </c>
       <c r="D7" t="n">
-        <v>1.185848316009084</v>
+        <v>5.436389452787407</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8446412205696106</v>
+        <v>-0.2023944223499294</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1423042298478086</v>
+        <v>8.969695066271132</v>
       </c>
       <c r="G7" t="n">
-        <v>2.527059186249971</v>
+        <v>5.436389452787407</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9665061831474304</v>
+        <v>-0.2023944223499294</v>
       </c>
       <c r="I7" t="n">
-        <v>5.225995555520058</v>
+        <v>1.638089975486208</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8795264959335327</v>
+        <v>2.78059713205487</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.650131552498609</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.8729317664758123</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6.189097934216262</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.07527932371783615</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>Polynomial</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"degree": 2, "alpha": 10.0}</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.030044838786125</v>
+        <v>9.152017384767532</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5699188057410153</v>
+        <v>4.750069616254988</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8217577576637268</v>
+        <v>-0.9252780079841614</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1325776839600701</v>
+        <v>9.808813855051994</v>
       </c>
       <c r="G8" t="n">
-        <v>4.597135558724403</v>
+        <v>4.866407459383236</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8503936290740967</v>
+        <v>-2.100792670249939</v>
       </c>
       <c r="I8" t="n">
-        <v>5.814818292856216</v>
+        <v>5.446867872689034</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8742733001708984</v>
+        <v>8.171669021248817</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.147700855776298</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.1963868498802185</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.637144833803177</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.3634794782642266</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Polynomial</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{"degree": 3, "alpha": 10.0}</t>
+          <t>{"n_estimators": 300, "max_depth": -1, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4.858193770051003</v>
+        <v>10.52375862252852</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8948549917713621</v>
+        <v>5.848936206855041</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8208396434783936</v>
+        <v>-0.942035150596972</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1590719625245934</v>
+        <v>10.46902718948822</v>
       </c>
       <c r="G9" t="n">
-        <v>3.420910909771919</v>
+        <v>5.894794697643841</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9257104396820068</v>
+        <v>-0.8390267871305588</v>
       </c>
       <c r="I9" t="n">
-        <v>6.113382056355476</v>
+        <v>2.744815598475084</v>
       </c>
       <c r="J9" t="n">
-        <v>0.850298285484314</v>
+        <v>8.815485862202879</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.307089012050564</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4220179798596185</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.653541327285337</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.5375220043055754</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GaussianProcess</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{"length_scale": 1.0, "noise": 0.1, "alpha": 1e-06}</t>
+          <t>{"n_estimators": 100, "max_depth": null, "min_samples_split": 2}</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5.206212631663956</v>
+        <v>11.06281624864909</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8301408217640737</v>
+        <v>6.271551391363723</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8274209580276499</v>
+        <v>-1.084752111482109</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1319680407346774</v>
+        <v>11.12157880806838</v>
       </c>
       <c r="G10" t="n">
-        <v>2.897358956098894</v>
+        <v>6.262546146130051</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9490866070032473</v>
+        <v>-1.083522074940364</v>
       </c>
       <c r="I10" t="n">
-        <v>6.27542537322046</v>
+        <v>3.07670910603866</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8489407164461956</v>
+        <v>2.886002383937165</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.3584426061792196</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8463782317114154</v>
+      </c>
+      <c r="M10" t="n">
+        <v>8.235576424131214</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.05688554752960501</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Linear</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"kernel": "rbf", "C": 100.0, "epsilon": 0.1, "gamma": "scale"}</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.693485230207443</v>
+        <v>10.80019328092372</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8753123905406748</v>
+        <v>5.452082064318764</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7025119185447692</v>
+        <v>-1.15186491395655</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2934106060903186</v>
+        <v>11.44894326169471</v>
       </c>
       <c r="G11" t="n">
-        <v>6.188110038638115</v>
+        <v>6.748681687157214</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7353027939796448</v>
+        <v>-1.206817890932542</v>
       </c>
       <c r="I11" t="n">
-        <v>8.278691023588181</v>
+        <v>3.16906635612959</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7268006801605225</v>
+        <v>10.33846439811996</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8.486612881485057</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1057774318441169</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.110478863574754</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.5715640988058512</v>
       </c>
     </row>
   </sheetData>
